--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -25735,7 +25735,7 @@
         </is>
       </c>
       <c r="E405" s="4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>4749700</v>
       </c>
       <c r="I405" s="5" t="n">
-        <v>18129</v>
+        <v>18060</v>
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>4749700</v>
       </c>
       <c r="L405" s="5" t="n">
-        <v>18129</v>
+        <v>18060</v>
       </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
@@ -32434,9 +32434,9 @@
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>J | 262呎 (1房)
+          <t>J | 263呎 (1房)
 $475万
-$18,129/呎
+$18,060/呎
 (25年-06月-17日)</t>
         </is>
       </c>

--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>5027600</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>19189</v>
+        <v>19116</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>5027600</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>19189</v>
+        <v>19116</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>8310100</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>19326</v>
+        <v>19371</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>8310100</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>19326</v>
+        <v>19371</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>4975700</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>18991</v>
+        <v>18919</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>4975700</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>18991</v>
+        <v>18919</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -29467,9 +29467,9 @@
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>K | 262呎 (1房)
+          <t>K | 263呎 (1房)
 $503万
-$19,189/呎
+$19,116/呎
 (25年-04月-02日)</t>
         </is>
       </c>
@@ -30032,9 +30032,9 @@
       </c>
       <c r="P10" s="20" t="inlineStr">
         <is>
-          <t>Q | 430呎 (3房)
+          <t>Q | 429呎 (3房)
 $831万
-$19,326/呎
+$19,371/呎
 (25年-10月-06日)</t>
         </is>
       </c>
@@ -32243,9 +32243,9 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>G | 262呎 (1房)
+          <t>G | 263呎 (1房)
 $498万
-$18,991/呎
+$18,919/呎
 (25年-12月-12日)</t>
         </is>
       </c>

--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>6091500</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>19400</v>
+        <v>19462</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>6091500</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>19400</v>
+        <v>19462</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -29499,9 +29499,9 @@
       </c>
       <c r="O7" s="20" t="inlineStr">
         <is>
-          <t>P | 314呎 (1房)
+          <t>P | 313呎 (1房)
 $609万
-$19,400/呎
+$19,462/呎
 (25年-06月-18日)</t>
         </is>
       </c>

--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>4913500</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>18754</v>
+        <v>18683</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>4913500</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>18754</v>
+        <v>18683</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
@@ -30867,9 +30867,9 @@
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>K | 262呎 (1房)
+          <t>K | 263呎 (1房)
 $491万
-$18,754/呎
+$18,683/呎
 (25年-07月-31日)</t>
         </is>
       </c>

--- a/files/九龙-红磡-The Haddon.xlsx
+++ b/files/九龙-红磡-The Haddon.xlsx
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="E430" s="4" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>5143600</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>18636</v>
+        <v>18569</v>
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>5143600</v>
       </c>
       <c r="L430" s="5" t="n">
-        <v>18636</v>
+        <v>18569</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
@@ -32577,9 +32577,9 @@
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>E | 276呎 (1房)
+          <t>E | 277呎 (1房)
 $514万
-$18,636/呎
+$18,569/呎
 (25年-08月-18日)</t>
         </is>
       </c>
